--- a/Results/Phase 2/Methanol/methanol water use results.xlsx
+++ b/Results/Phase 2/Methanol/methanol water use results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1706479436131995</v>
+        <v>0.1671496296205597</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3041558645098824</v>
+        <v>0.247305067074639</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3040608732884616</v>
+        <v>0.2445638002366073</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2868917596685612</v>
+        <v>0.2361336557297689</v>
       </c>
       <c r="F33" t="n">
-        <v>0.294271175886457</v>
+        <v>0.2381528011528505</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1771780089268876</v>
+        <v>0.1710612302515885</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1789891290964686</v>
+        <v>0.1715956586559502</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2261052123653427</v>
+        <v>0.1990149830049613</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1894079898776071</v>
+        <v>0.17817768468047</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1931235258294088</v>
+        <v>0.1800537489718761</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1924096011313697</v>
+        <v>0.1799831897949447</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1917993194637976</v>
+        <v>0.1791295799919634</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1690549993134845</v>
+        <v>0.1660325737156898</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2070059729828138</v>
+        <v>0.2022006480864535</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1842267358685852</v>
+        <v>0.1753896831344661</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1682659751873454</v>
+        <v>0.1655543238509561</v>
       </c>
       <c r="R33" t="n">
-        <v>0.219365786478548</v>
+        <v>0.1949342647347181</v>
       </c>
       <c r="S33" t="n">
-        <v>0.1971739672418533</v>
+        <v>0.1831364614381547</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1717901030379812</v>
+        <v>0.1675672743724617</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2306814208699322</v>
+        <v>0.2161972155479356</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1895048785065095</v>
+        <v>0.1786272691902315</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2209775029381373</v>
+        <v>0.2119435445737173</v>
       </c>
       <c r="X33" t="n">
-        <v>0.194866410587672</v>
+        <v>0.1811097273686968</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.177134035900161</v>
+        <v>0.170849134403055</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1949790912929033</v>
+        <v>0.1895427976709748</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.220718119938925</v>
+        <v>0.1966259851900457</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1735599509015127</v>
+        <v>0.1684778037157893</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1620216120958476</v>
+        <v>0.1613113207271269</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2741191171622465</v>
+        <v>0.2305987326255966</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1853323320554333</v>
+        <v>0.1751842257184882</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2356955484937374</v>
+        <v>0.2059865148158699</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2960008006191913</v>
+        <v>0.2403474982602644</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1682671229081072</v>
+        <v>0.1651838190258386</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1803768226101353</v>
+        <v>0.1718668523905406</v>
       </c>
       <c r="I33" t="n">
-        <v>0.18371481282219</v>
+        <v>0.1740078201615432</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1833398435443898</v>
+        <v>0.1741455184229547</v>
       </c>
       <c r="K33" t="n">
-        <v>0.188157822042198</v>
+        <v>0.1773490454842062</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1991370380027206</v>
+        <v>0.1842028005399794</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1953612256394613</v>
+        <v>0.181039979579399</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1658294880208546</v>
+        <v>0.1635357105766996</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2096561651639799</v>
+        <v>0.2038075391356498</v>
       </c>
       <c r="P33" t="n">
-        <v>0.18394162073599</v>
+        <v>0.1749223046798847</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1632473762153008</v>
+        <v>0.1620263691810742</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1873008821130217</v>
+        <v>0.1759292475033153</v>
       </c>
       <c r="S33" t="n">
-        <v>0.1962786114423326</v>
+        <v>0.1825444010030838</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1725434795926792</v>
+        <v>0.1674296848963574</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2127192837340469</v>
+        <v>0.2050414880402008</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1795146639113386</v>
+        <v>0.1721561300590175</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2109237584067877</v>
+        <v>0.2052519313999951</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1958492584443331</v>
+        <v>0.1815921359300383</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1673655073951298</v>
+        <v>0.1644567837302228</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.183350300492703</v>
+        <v>0.1814033712663159</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.1794299326432421</v>
+        <v>0.1716036226431096</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.173714443824306</v>
+        <v>0.1680167485682103</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1692858419875441</v>
+        <v>0.1663852806125424</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2983272098173406</v>
+        <v>0.244675140721861</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2509357221556278</v>
+        <v>0.2137089090107667</v>
       </c>
       <c r="E33" t="n">
-        <v>0.281831774180638</v>
+        <v>0.2331984553224455</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3031678539754129</v>
+        <v>0.244078527474852</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1765171890452718</v>
+        <v>0.1707475872400191</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1846395703218619</v>
+        <v>0.1749175668598175</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2372230064883783</v>
+        <v>0.2055223518559236</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1898473129538231</v>
+        <v>0.1785473338072954</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1974401518977169</v>
+        <v>0.1831598546755543</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1998045267626259</v>
+        <v>0.1844493817618091</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1919345236545224</v>
+        <v>0.1793080804541247</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1689824022521587</v>
+        <v>0.1660553730999276</v>
       </c>
       <c r="O33" t="n">
-        <v>0.211320508146326</v>
+        <v>0.2054837496238005</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1842464560589271</v>
+        <v>0.1754758597566328</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1684422313360523</v>
+        <v>0.1657286403425579</v>
       </c>
       <c r="R33" t="n">
-        <v>0.217186596064276</v>
+        <v>0.1937456388457101</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2054063578835847</v>
+        <v>0.188270711918761</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1715770798408636</v>
+        <v>0.1675173320894517</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2277424792140451</v>
+        <v>0.2145738970598073</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1914348409156597</v>
+        <v>0.1800972486245593</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2181004833938618</v>
+        <v>0.2103621071342992</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1961024484460202</v>
+        <v>0.1819361040053492</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1770521607649952</v>
+        <v>0.1708946233133999</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1946259522779923</v>
+        <v>0.1894321344399055</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.209979563884192</v>
+        <v>0.1904255643483697</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1734466911616805</v>
+        <v>0.168479779827594</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.167708670276086</v>
+        <v>0.1651528365202801</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2703853792202939</v>
+        <v>0.2284208748729582</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2172452910948934</v>
+        <v>0.1939463519378542</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2477899650586929</v>
+        <v>0.2121702241548188</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2925568895819728</v>
+        <v>0.2380836880297923</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1747978294422015</v>
+        <v>0.1694839917251007</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1819795214695722</v>
+        <v>0.1730849983923017</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1993545925830938</v>
+        <v>0.1833424637803903</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1856211641486108</v>
+        <v>0.1758000292478089</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1901265179716414</v>
+        <v>0.1787917759649205</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1970044734326227</v>
+        <v>0.182555595928751</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1847297939150796</v>
+        <v>0.1748428072517144</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1674255960791061</v>
+        <v>0.1648667487117894</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2129037044337495</v>
+        <v>0.2064712631890551</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1822696275671074</v>
+        <v>0.1740678206043171</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1681343978326024</v>
+        <v>0.165300719541869</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2152447824643155</v>
+        <v>0.192348200499658</v>
       </c>
       <c r="S33" t="n">
-        <v>0.1948781497928983</v>
+        <v>0.1816882155085962</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1735043456714429</v>
+        <v>0.1683612528810801</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2161317987853517</v>
+        <v>0.2074896234115622</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1884531272206471</v>
+        <v>0.1780852607670831</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2167708428570519</v>
+        <v>0.2094721425144601</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1962557008951847</v>
+        <v>0.1817919519893512</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1750628217187429</v>
+        <v>0.1694386375549614</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1923517787228229</v>
+        <v>0.1879649983277199</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.1951355048620494</v>
+        <v>0.1813254116932617</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1749040815474511</v>
+        <v>0.1690232495279194</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1666056619528591</v>
+        <v>0.1642658599742653</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2725010636531201</v>
+        <v>0.2297678586839044</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2042609247092943</v>
+        <v>0.1865054478776522</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2366822810187887</v>
+        <v>0.2063679079622579</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2760888030011045</v>
+        <v>0.2284128317537132</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1727607827006306</v>
+        <v>0.1680705690776639</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1781968857411275</v>
+        <v>0.1706468638480014</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1859508392347013</v>
+        <v>0.1754011232246793</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1835813011597692</v>
+        <v>0.1743969327542635</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1841733258572885</v>
+        <v>0.1749118308150319</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1954133924639984</v>
+        <v>0.1816515823025809</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1880829645801783</v>
+        <v>0.1767726987974539</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1661091936521576</v>
+        <v>0.1638359022436101</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2094772701543991</v>
+        <v>0.2038748986315613</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1777127796083307</v>
+        <v>0.1711577017690313</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1680912845715463</v>
+        <v>0.1650580498844826</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2028273119941103</v>
+        <v>0.1849313227052586</v>
       </c>
       <c r="S33" t="n">
-        <v>0.1905006254709932</v>
+        <v>0.1788708202846749</v>
       </c>
       <c r="T33" t="n">
-        <v>0.174024209839654</v>
+        <v>0.168403168754182</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2086533335759134</v>
+        <v>0.2027597071283017</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1839467303873996</v>
+        <v>0.1750981267670983</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2131740736678074</v>
+        <v>0.207022265562845</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1960267089256815</v>
+        <v>0.1816444797206804</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1718756293042465</v>
+        <v>0.1672561451748909</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1886549894325056</v>
+        <v>0.1853679046152807</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.1878005376333218</v>
+        <v>0.1766920661511871</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1739769353686884</v>
+        <v>0.1682675979201974</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1646880047248166</v>
+        <v>0.1637685234799868</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3128060176189622</v>
+        <v>0.2538292192642013</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2147626788920879</v>
+        <v>0.1930645135635758</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2929027797418181</v>
+        <v>0.2401344449490815</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3293162343648304</v>
+        <v>0.2603664707023287</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1714257022745942</v>
+        <v>0.1679710286639023</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1903069808723956</v>
+        <v>0.1784194947191589</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2424843832220198</v>
+        <v>0.2090270878707089</v>
       </c>
       <c r="J33" t="n">
-        <v>0.194326848281089</v>
+        <v>0.18166342805147</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2056351644016954</v>
+        <v>0.1886116555238961</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2130329076525821</v>
+        <v>0.1939111955784328</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2235485551491599</v>
+        <v>0.1992845179396352</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1700108081261357</v>
+        <v>0.1669203573277235</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2153297234188924</v>
+        <v>0.208758251516133</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1935493842452871</v>
+        <v>0.1814152273874033</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1677855891549931</v>
+        <v>0.1655951448118947</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2162900271206102</v>
+        <v>0.1934570184488753</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2261801130356948</v>
+        <v>0.2030574641852469</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1759717483342797</v>
+        <v>0.1704224093711314</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2218404479279891</v>
+        <v>0.2114261269307463</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1928525395869924</v>
+        <v>0.1812114287644656</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2263345538339688</v>
+        <v>0.2156308936355466</v>
       </c>
       <c r="X33" t="n">
-        <v>0.2000326417529688</v>
+        <v>0.184550738612711</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1776024523630078</v>
+        <v>0.1714464409960895</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1932536340546533</v>
+        <v>0.1887395835744473</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.2180021112652406</v>
+        <v>0.1954234365275305</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.2023921719556716</v>
+        <v>0.1856167319233284</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1629196549977413</v>
+        <v>0.161998190680234</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2788740540883757</v>
+        <v>0.2335599336952687</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1889666236965733</v>
+        <v>0.1775879329590108</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2379850335083251</v>
+        <v>0.2062199201502853</v>
       </c>
       <c r="F33" t="n">
-        <v>0.291067837386777</v>
+        <v>0.2379755101792304</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1675984564698971</v>
+        <v>0.1649338973791198</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1817938548094065</v>
+        <v>0.172826529423656</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1959726000958801</v>
+        <v>0.1814202183166757</v>
       </c>
       <c r="J33" t="n">
-        <v>0.184509105801974</v>
+        <v>0.1751639653797106</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1844225668673254</v>
+        <v>0.1751427763893494</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1862255397155668</v>
+        <v>0.1770326930415184</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1973721219464525</v>
+        <v>0.1832985195330805</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1679136060143114</v>
+        <v>0.1649728881551278</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2130666178227449</v>
+        <v>0.2062770074997791</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1895099825467647</v>
+        <v>0.1783547179291145</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1641186102424634</v>
+        <v>0.1627070916271168</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1945246417954717</v>
+        <v>0.1803861731852597</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2032037738651531</v>
+        <v>0.1876195024865385</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1711398210796334</v>
+        <v>0.1668716021088871</v>
       </c>
       <c r="U33" t="n">
-        <v>0.215732443904712</v>
+        <v>0.2074480017837589</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1855427667375631</v>
+        <v>0.1761372356151636</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2155290205849946</v>
+        <v>0.2084995453055614</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1925580533152787</v>
+        <v>0.1798220700028897</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1722668670910057</v>
+        <v>0.1675191287411039</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1858089826681899</v>
+        <v>0.183231254358496</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.1837645583879331</v>
+        <v>0.1743592513082185</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1873169899350852</v>
+        <v>0.1763572201568444</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1618519241345268</v>
+        <v>0.1607767772813529</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2656920040930302</v>
+        <v>0.224720109644417</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1825955452563661</v>
+        <v>0.1730702041204334</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1905042850223002</v>
+        <v>0.1772479941504767</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2712542772593321</v>
+        <v>0.2249440511118918</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1636589266102278</v>
+        <v>0.1618886791434249</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1759821603510456</v>
+        <v>0.1688809814010818</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1766147275575286</v>
+        <v>0.1693657158773391</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1777691588241416</v>
+        <v>0.1703320354457978</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1749431966191623</v>
+        <v>0.1686277073075279</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1827831003586331</v>
+        <v>0.1739605305521242</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1870506659117253</v>
+        <v>0.1757984197577688</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1641574219772081</v>
+        <v>0.1621133236155794</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2074328364584364</v>
+        <v>0.2015680374223488</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1853459811316166</v>
+        <v>0.1753809933810363</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.161717517816555</v>
+        <v>0.1606596468631544</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1820534260183607</v>
+        <v>0.1724369585749398</v>
       </c>
       <c r="S33" t="n">
-        <v>0.1927753958348855</v>
+        <v>0.179991748414508</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1683094268432078</v>
+        <v>0.1645345267464809</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2095932300295964</v>
+        <v>0.2026401429046174</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1772585151959586</v>
+        <v>0.1703150471162069</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2057738877309828</v>
+        <v>0.2016412468877887</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1848089515105148</v>
+        <v>0.1746524223229296</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1679781268908364</v>
+        <v>0.1643581771374785</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1807069379992605</v>
+        <v>0.1793143049140783</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.1694006393366533</v>
+        <v>0.165220766600835</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1750395640177708</v>
+        <v>0.1683603296093934</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1674116191060715</v>
+        <v>0.165375848625908</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3078933578585973</v>
+        <v>0.2506924997050075</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2578285206204757</v>
+        <v>0.217870312144203</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2865190822411787</v>
+        <v>0.2361732121375788</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3175711166984746</v>
+        <v>0.2530707266945997</v>
       </c>
       <c r="G33" t="n">
-        <v>0.176469864376891</v>
+        <v>0.1709626564056548</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1872777834321793</v>
+        <v>0.1765912001464828</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2314562346113158</v>
+        <v>0.2025214742210634</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1913945855922859</v>
+        <v>0.17974496742066</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2018624613777721</v>
+        <v>0.1862737113153561</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2053396533976751</v>
+        <v>0.1882281105662178</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1919698623012909</v>
+        <v>0.1799746645331937</v>
       </c>
       <c r="N33" t="n">
-        <v>0.168666888207834</v>
+        <v>0.166017372727005</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2114055949817016</v>
+        <v>0.2057392131492168</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1853950768808031</v>
+        <v>0.1763201599493094</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1675515441217483</v>
+        <v>0.1653673225405876</v>
       </c>
       <c r="R33" t="n">
-        <v>0.2116083126883424</v>
+        <v>0.1906827281181866</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2097283491704403</v>
+        <v>0.1917224968339741</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1716068420291492</v>
+        <v>0.1676852926350552</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2252092748301779</v>
+        <v>0.2133084204438819</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1927342902663995</v>
+        <v>0.1810636635985014</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2242870774239144</v>
+        <v>0.2143295120037979</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1987387810943567</v>
+        <v>0.1836375628311191</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1775165164602459</v>
+        <v>0.1713241761436834</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1943063287272873</v>
+        <v>0.1893508701332492</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.2165308838290997</v>
+        <v>0.1944774225710834</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1845746042573237</v>
+        <v>0.1750145139495516</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1633884179301703</v>
+        <v>0.1626099287843815</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2797014533428011</v>
+        <v>0.2343454251319617</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2065613208805112</v>
+        <v>0.1880630492618094</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2539872969993565</v>
+        <v>0.2161252779476892</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3076306074207735</v>
+        <v>0.2477277541247857</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1731727673285699</v>
+        <v>0.1687114644302362</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1840926009043453</v>
+        <v>0.1743992349195123</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2048430841368939</v>
+        <v>0.1866786817372264</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1898100268217355</v>
+        <v>0.1785797368022273</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1929487793787224</v>
+        <v>0.180739540110964</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1973175941040171</v>
+        <v>0.1835487781129078</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2174452855348906</v>
+        <v>0.1952289800244182</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1671884758508704</v>
+        <v>0.1648263563553801</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2129934714471655</v>
+        <v>0.2067292139131732</v>
       </c>
       <c r="P33" t="n">
-        <v>0.1855450848199935</v>
+        <v>0.1762347257224167</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.165666481243117</v>
+        <v>0.163966329394497</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1978972439354525</v>
+        <v>0.1824930829673962</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2006604379281272</v>
+        <v>0.1858646073060088</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1715988326915837</v>
+        <v>0.1673775946989952</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2197110892286147</v>
+        <v>0.2098718350821986</v>
       </c>
       <c r="V33" t="n">
-        <v>0.1867165727349039</v>
+        <v>0.1771263075514832</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2179156235140524</v>
+        <v>0.210092860511195</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1987804375187396</v>
+        <v>0.1836107844439948</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1741911211713829</v>
+        <v>0.1690242163864657</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.1875730638948012</v>
+        <v>0.1846155070925511</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.1978267063418954</v>
+        <v>0.1830274522706254</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.1832183233520878</v>
+        <v>0.1740137653473188</v>
       </c>
     </row>
   </sheetData>
